--- a/NCLH_model_v6.xlsx
+++ b/NCLH_model_v6.xlsx
@@ -125,7 +125,7 @@
     <t xml:space="preserve">Thesis to KPIs</t>
   </si>
   <si>
-    <t xml:space="preserve">Start here: data -&gt; KPI -&gt; model -&gt; consensus, with dated checks</t>
+    <t xml:space="preserve">Start here: data -&gt; KPI -&gt; model -&gt; consensus, with dated checks and critiques</t>
   </si>
   <si>
     <t xml:space="preserve">DCF</t>
